--- a/artfynd/A 20098-2025 artfynd.xlsx
+++ b/artfynd/A 20098-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124825262</v>
+        <v>124825260</v>
       </c>
       <c r="B2" t="n">
         <v>78547</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511329</v>
+        <v>511300</v>
       </c>
       <c r="R2" t="n">
-        <v>6851464</v>
+        <v>6851490</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124825261</v>
+        <v>124825262</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511300</v>
+        <v>511329</v>
       </c>
       <c r="R3" t="n">
-        <v>6851490</v>
+        <v>6851464</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124825260</v>
+        <v>124825261</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 20098-2025 artfynd.xlsx
+++ b/artfynd/A 20098-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124825260</v>
+        <v>124825261</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124825261</v>
+        <v>124825260</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 20098-2025 artfynd.xlsx
+++ b/artfynd/A 20098-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124825261</v>
+        <v>124825262</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511300</v>
+        <v>511329</v>
       </c>
       <c r="R2" t="n">
-        <v>6851490</v>
+        <v>6851464</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124825262</v>
+        <v>124825260</v>
       </c>
       <c r="B3" t="n">
         <v>78547</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511329</v>
+        <v>511300</v>
       </c>
       <c r="R3" t="n">
-        <v>6851464</v>
+        <v>6851490</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124825260</v>
+        <v>124825261</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 20098-2025 artfynd.xlsx
+++ b/artfynd/A 20098-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124825262</v>
+        <v>124825260</v>
       </c>
       <c r="B2" t="n">
         <v>78547</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511329</v>
+        <v>511300</v>
       </c>
       <c r="R2" t="n">
-        <v>6851464</v>
+        <v>6851490</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124825260</v>
+        <v>124825262</v>
       </c>
       <c r="B3" t="n">
         <v>78547</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511300</v>
+        <v>511329</v>
       </c>
       <c r="R3" t="n">
-        <v>6851490</v>
+        <v>6851464</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 20098-2025 artfynd.xlsx
+++ b/artfynd/A 20098-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124825262</v>
+        <v>124825261</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511329</v>
+        <v>511300</v>
       </c>
       <c r="R3" t="n">
-        <v>6851464</v>
+        <v>6851490</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124825261</v>
+        <v>124825262</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511300</v>
+        <v>511329</v>
       </c>
       <c r="R4" t="n">
-        <v>6851490</v>
+        <v>6851464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 20098-2025 artfynd.xlsx
+++ b/artfynd/A 20098-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124825260</v>
+        <v>124825262</v>
       </c>
       <c r="B2" t="n">
         <v>78547</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511300</v>
+        <v>511329</v>
       </c>
       <c r="R2" t="n">
-        <v>6851490</v>
+        <v>6851464</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124825262</v>
+        <v>124825260</v>
       </c>
       <c r="B4" t="n">
         <v>78547</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511329</v>
+        <v>511300</v>
       </c>
       <c r="R4" t="n">
-        <v>6851464</v>
+        <v>6851490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 20098-2025 artfynd.xlsx
+++ b/artfynd/A 20098-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124825262</v>
+        <v>124825261</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511329</v>
+        <v>511300</v>
       </c>
       <c r="R2" t="n">
-        <v>6851464</v>
+        <v>6851490</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124825261</v>
+        <v>124825262</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511300</v>
+        <v>511329</v>
       </c>
       <c r="R3" t="n">
-        <v>6851490</v>
+        <v>6851464</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 20098-2025 artfynd.xlsx
+++ b/artfynd/A 20098-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124825260</v>
+        <v>124825261</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124825261</v>
+        <v>124825260</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 20098-2025 artfynd.xlsx
+++ b/artfynd/A 20098-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825262</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>124825261</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>78683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>124825260</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
